--- a/scripture-creations/catalog.xlsx
+++ b/scripture-creations/catalog.xlsx
@@ -1,22 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ScriptureCreations\Marketing\WebSite\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Code\Websites\Reed\scripture-creations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA78F98C-E9CC-4D17-BE28-02B8C2DDD663}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F5EAE1-FFC1-4D8E-B504-ABB7D9BB79E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{82252E67-CF23-4A4C-8DD5-12847BD7CFFE}"/>
+    <workbookView xWindow="-156" yWindow="1560" windowWidth="17280" windowHeight="8880" xr2:uid="{82252E67-CF23-4A4C-8DD5-12847BD7CFFE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -26,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="167">
   <si>
     <t>id</t>
   </si>
@@ -79,15 +78,9 @@
     <t>SignsOfTimes.jpg</t>
   </si>
   <si>
-    <t>This chart shows 129 prophecies in relationship to the church, the house of Israel, and the world in general.  A concise overview of the times we are living in and the signs of the second coming of Jesus Christ.  Laminated.</t>
-  </si>
-  <si>
     <t>Missionary Pack (9 bookmarks)</t>
   </si>
   <si>
-    <t xml:space="preserve">Includes: Plan of Salvation, Evidences for Joseph Smith, Evidences for the B. of M., Points of Christ’s True Church, Prophecies Fulfilled by Jesus Christ, Daniel’s Vision of the Restoration, Introduction to The Church of Jesus Christ of Latter-day Saints, Eternal Rewards, LDS Doctrine of Deity, and Book of Mormon study map. </t>
-  </si>
-  <si>
     <t>Doctrine of Deity Pamphlet.jpg</t>
   </si>
   <si>
@@ -100,9 +93,6 @@
     <t>BofMTimeLineFront.jpg</t>
   </si>
   <si>
-    <t>A time line of Book of Mormon events and people.  Has the authors of the Books in the Book of Mormon and when they wrote.  Has a quick reference for the major stories, events, and quoted scriptures in the Book of Mormon.  Laminated.</t>
-  </si>
-  <si>
     <t>Genealogy of the 12 Tribes Bookmark</t>
   </si>
   <si>
@@ -112,18 +102,12 @@
     <t>Genealogy of 12 Tribes Sm.jpg</t>
   </si>
   <si>
-    <t>Shows family relationships for Abraham, Isaac, Jacob, &amp; his sons.  Shows from whom the Moabites, Edomites, &amp; Children of Ammon descended.  The back defines the Abrahamic covenant.  Laminated.</t>
-  </si>
-  <si>
     <t>Old Testament Chrolonology Bookmark</t>
   </si>
   <si>
     <t>OTBookmarkFront.jpg</t>
   </si>
   <si>
-    <t>This bookmark shows a time line of Old Testament events and people.  It shows the patriarchs' births and how long they lived.  Identifies roles of the leaders in Israel and Judah.  Laminated.</t>
-  </si>
-  <si>
     <t>New Testament Study Map Bookmark</t>
   </si>
   <si>
@@ -136,9 +120,6 @@
     <t>New Testament Study Map Chart</t>
   </si>
   <si>
-    <t xml:space="preserve">A 8.5 x 11" map of the New Testament area with pictures of many events of Christ's life at the locations where they happened.  The Map lists all of Jesus Christ's parables, miracles, and events.  Laminated. </t>
-  </si>
-  <si>
     <t xml:space="preserve">A 4.75" x 7" map of the New Testament area with pictures of many events of Christ's life at the locations where they happened.  Laminated. </t>
   </si>
   <si>
@@ -148,36 +129,24 @@
     <t>ParablesSm.jpg</t>
   </si>
   <si>
-    <t>This bookmark lists all the parables of Jesus Christ that are recorded in the New Testament with their references.   Laminated.</t>
-  </si>
-  <si>
     <t>Miracles of Jesus Christ</t>
   </si>
   <si>
     <t>MiraclesOfJesusChristBackground.jpg</t>
   </si>
   <si>
-    <t>This bookmark lists all the miracles Jesus performed that are recorded in the New Testament with their references.    Laminated</t>
-  </si>
-  <si>
     <t>Revelations Condensed Bookmark</t>
   </si>
   <si>
     <t>Revelations Condensed.jpg</t>
   </si>
   <si>
-    <t>This bookmark condenses the Book of Revelations to provide a list of 107 events leading up to Christ's second coming.  Laminated.</t>
-  </si>
-  <si>
     <t>Book of Mormon and the American Indian Chart</t>
   </si>
   <si>
     <t>BofM-Indians.jpg</t>
   </si>
   <si>
-    <t>This 8.5" x 11" Chart combines the prophecies about the American Indians into one concice chart.  Who are they?  Prophecies of the gentiles coming.  Why were they destroyed as a people?  What is their future?  Laminated.</t>
-  </si>
-  <si>
     <t>Plan of Salvation Bookmark</t>
   </si>
   <si>
@@ -211,9 +180,6 @@
     <t>Church History Study Map Chart</t>
   </si>
   <si>
-    <t>A 8.5z' x 11" map of the United States with locations and events that transpired as church history unfolded.  It shows where each section of the D&amp;C was recieved. The back has the chronology of the early church history.  Laminated.</t>
-  </si>
-  <si>
     <t>A 4.75" x 7" map of the United States with locations and events that transpired as church history unfolded.  It shows where each section of the D&amp;C was recieved. The back has the chronology of the early church history.  Laminated.</t>
   </si>
   <si>
@@ -223,18 +189,12 @@
     <t>EternalRewards.jpg</t>
   </si>
   <si>
-    <t>This bookmark summarizes D&amp;C 76 and contrasts the  telestial, terrestrial, and celestial kingdoms and shows the requirements and rewards for each kingdom.  Laminated.</t>
-  </si>
-  <si>
     <t>Evidences for Joseph Smith Bookmark</t>
   </si>
   <si>
     <t>EvidencesForJSMarketingSmall.jpg</t>
   </si>
   <si>
-    <t>This bookmark lists many of the things that Joseph Smith did that are evidences that he truly was a prophet of God.   Laminated.</t>
-  </si>
-  <si>
     <t>Book of Mormon Study Map Chart</t>
   </si>
   <si>
@@ -256,9 +216,6 @@
     <t>Genealogy of the 12 Tribes Chart</t>
   </si>
   <si>
-    <t>Yard Signs of Jesus</t>
-  </si>
-  <si>
     <t>Box Top.jpg</t>
   </si>
   <si>
@@ -298,108 +255,69 @@
     <t>AbrahamicCovenantMarketing.jpg</t>
   </si>
   <si>
-    <t>This chart explains the Abrahamic Covenant, who it is to and what it is.   Laminated.</t>
-  </si>
-  <si>
     <t>The Lost 10 Tribes Chart</t>
   </si>
   <si>
     <t>LostTribesMarketing.jpg</t>
   </si>
   <si>
-    <t>This chart lists what we know of the lost tribes, where they went, where they are, when and how will they return.   Laminated.</t>
-  </si>
-  <si>
     <t>Miracles of the Old Testament Bookmark</t>
   </si>
   <si>
     <t>Miracles of the OT.jpg</t>
   </si>
   <si>
-    <t>This bookmark lists the miracles recorded in the Old Testament with their scripture references.  Laminated.</t>
-  </si>
-  <si>
     <t>Events of the Old Testament Bookmark</t>
   </si>
   <si>
     <t>events-of-the-old-testament-bookmark.jpg</t>
   </si>
   <si>
-    <t>This bookmark is designed as a quick reference for major events that happened in the Old Testament and their scripture references.  Laminated.</t>
-  </si>
-  <si>
     <t>Daniel's Vision of the Restoration Bookmark</t>
   </si>
   <si>
     <t>Daniels Vision.jpg</t>
   </si>
   <si>
-    <t>This bookmark shows how Daniel saw the year when Joseph Smith would complete the restoration and “the sanctuary” would be cleansed.    Laminated.</t>
-  </si>
-  <si>
     <t>Prophecies Fulfilled by Jesus Christ Bkmrk</t>
   </si>
   <si>
     <t>PropheciesOfChristMarketing.jpg</t>
   </si>
   <si>
-    <t>This bookmark lists many of the prophecies about Jesus Christ recorded in the Old Testament with their scripture references.  Laminated.</t>
-  </si>
-  <si>
     <t>Events of the New Testament Bookmark</t>
   </si>
   <si>
     <t>NTEvents.jpg</t>
   </si>
   <si>
-    <t>This bookmark lists many major events in the New Testament, their locations, and the scripture reference.    Laminated.</t>
-  </si>
-  <si>
     <t>Points of Christ's True Church Bookmark</t>
   </si>
   <si>
     <t>Points of Christs True Church.jpg</t>
   </si>
   <si>
-    <t>This bookmark lists 48 doctrines that were taught by Jesus and his disciples that should exist in His church today.  All references are from the Bible.  Laminated.</t>
-  </si>
-  <si>
-    <t>10 beautiful 12" x 18" yard signs with H-stakes showing images of Jesus. Great for showing your love for Jesus Christ at Christmas, Easter, or anytime.  ($15 per sign)</t>
-  </si>
-  <si>
     <t>Evidences for the Book of Mormon Bookmark</t>
   </si>
   <si>
     <t>EvidencesForBofMMarketing.jpg</t>
   </si>
   <si>
-    <t>This bookmark lists many of the evidences for the Book of Mormon.  Laminated.</t>
-  </si>
-  <si>
     <t>Miracles of the Book of Mormon Bookmark</t>
   </si>
   <si>
     <t>Book of Mormon Miracles.jpg</t>
   </si>
   <si>
-    <t>Lists many of the miracles spoken of in the Book of Mormon.  Laminated.</t>
-  </si>
-  <si>
     <t>People of the Book of Mormon Chart</t>
   </si>
   <si>
     <t>People of BofM.jpg</t>
   </si>
   <si>
-    <t>List all the people in the Book of Mormon (non-Jaradite) in the chronological order they are mentioned.  It indicates their main roles and affiliations.  A great Book of Mormon overview and study help. Laminated.</t>
-  </si>
-  <si>
     <t>QuickReferenceMarketingSm.jpg</t>
   </si>
   <si>
-    <t>A bookmark that lists church doctrine and oft quoted scriptures and where to find them in the Doctrine and Covenants.  Laminated.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Doctrine and Covenants Quick Reference Bookmark </t>
   </si>
   <si>
@@ -409,9 +327,6 @@
     <t>PriesthoodSm.jpg</t>
   </si>
   <si>
-    <t>This bookmark lists the offices, quorums, and duties of the Aaronic &amp; Melchizedek Priesthood and includes the scripture references associated with each office.  Laminated.</t>
-  </si>
-  <si>
     <t>Evidences for Joseph Smith &amp; Book of Mormon</t>
   </si>
   <si>
@@ -424,42 +339,24 @@
     <t>Introduction to the Church of Jesus Christ of Latter-day Saints Bookmark</t>
   </si>
   <si>
-    <t>This bookmark is designed as a pass along card to share LDS beliefs with those who would like to know more about the Church of Jesus Christ of Latter-day Saints. Laminated.</t>
-  </si>
-  <si>
     <t>Introduction to the Church of Jesus Christ of Latter-day Saints 10-pack</t>
   </si>
   <si>
     <t>2500 Signs of the Times in Chronological Order ebook</t>
   </si>
   <si>
-    <t>Ri Conquers the Multiverse ebook</t>
-  </si>
-  <si>
-    <t>Criticism to Gratitude Tracker Chart</t>
-  </si>
-  <si>
     <t>Book of Mormon Study Map Wall Chart</t>
   </si>
   <si>
-    <t>19" x 26" wall map of the relative geography of the Book of Mormon.  Map have a gazetteer and scriptures mentioning each location on the back to help find locations. Laminated.</t>
-  </si>
-  <si>
     <t>These cards are designed to share LDS beliefs with those who would like to know more about the Church of Jesus Christ of Latter-day Saints. Pack of 10 cards to leave out on your desk or wherever those interested can find them or pass along to someone who might be interested.  Laminated.</t>
   </si>
   <si>
-    <t>Picture Puzzle</t>
-  </si>
-  <si>
     <t>2500Signs.jpg</t>
   </si>
   <si>
     <t>Introduction to Church.jpg</t>
   </si>
   <si>
-    <t>Images of Jesus Coloring Book</t>
-  </si>
-  <si>
     <t>Getting Satan Out of Your Marriage Pamphlet</t>
   </si>
   <si>
@@ -472,9 +369,6 @@
     <t>Deep State Image.jpg</t>
   </si>
   <si>
-    <t>MarriagePamphlet.jpeg</t>
-  </si>
-  <si>
     <t>This book gives a comprehensive list of scriptures about future events. It takes Revelation, Mathew 24, Luke 20, and JS Mathew as a skeleton and adds in all the other references attempting to keep them in the order given in each chapter. Great for a deep dive into the Signs of Christ's coming.</t>
   </si>
   <si>
@@ -484,34 +378,154 @@
     <t>Coloring book with 20 pictures and titles of Jesus. 8.5" x 11"</t>
   </si>
   <si>
-    <t>10 pictures of Jesus with small snips from the pictures to match with the pictures, with three levels of dificulty.</t>
-  </si>
-  <si>
     <t>Shouldn't marital problems be solved through the gospel of Jesus Christ? How much of the conflict comes from not being Christ-like? This is a two week program to catapult your relationship from frustrating to fantastic.</t>
   </si>
   <si>
     <t>How happy can you be? Non-judgmental, non-critical, forgiving, and grateful make for a happy marriage and life. This is a chart for helping move your life to amazing. "whoso is happy, will be happy still…." --Mormon 9:14</t>
   </si>
   <si>
-    <t>A ward challenge. Can you do the temple work for enough people to fill a spirit world chapel? Add a dot for each ordinance done and see their chapel fill.</t>
-  </si>
-  <si>
     <t>Follow a young intelligence as he learns and grows while moving through worlds of his progression. A little "coming of age", a little "a boy and his dog" and a little romance. "Ri Conquers the Multiverse" will change your view your life.</t>
   </si>
   <si>
-    <t>Fill a Spirit Ward</t>
-  </si>
-  <si>
     <t>Coloring Book Front for Marketing.jpg</t>
   </si>
   <si>
-    <t>Fill a Chapel.jpg</t>
-  </si>
-  <si>
-    <t>Front Page - Criticism to Gratitude.jpg</t>
-  </si>
-  <si>
     <t>Puzzle 1 Cover.jpg</t>
+  </si>
+  <si>
+    <t>Picture Puzzle #1</t>
+  </si>
+  <si>
+    <t>Images of Jesus Coloring Book -Book 1</t>
+  </si>
+  <si>
+    <t>Ri Conquers the Multiverse - ebook</t>
+  </si>
+  <si>
+    <t>Titles of Jesus Yard Signs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Includes: Plan of Salvation, Evidences for Joseph Smith, Evidences for the Book of Mormon, Points of Christ’s True Church, Prophecies Fulfilled by Jesus Christ, Daniel’s Vision of the Restoration, Introduction to The Church of Jesus Christ of Latter-day Saints, Eternal Rewards, LDS Doctrine of Deity, and a Book of Mormon study map. </t>
+  </si>
+  <si>
+    <t>19" x 26" wall map of the relative geography of the Book of Mormon.  Map have a gazetteer and a comprehensive list of scriptures mentioning each location on the back to help find locations. Laminated.</t>
+  </si>
+  <si>
+    <t>A time line of Book of Mormon events and people.  It lists the authors of the Books in the Book of Mormon and when they wrote.  Has a quick reference for the major stories, events, and quoted scriptures in the Book of Mormon.  Laminated.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A 8.5 x 11" map of the New Testament area with pictures of many events of Christ's life at the locations where they happened.  The Map back gives references for all of Jesus Christ's parables, miracles, and events.  Laminated. </t>
+  </si>
+  <si>
+    <t>This 8.5" x 11" Chart combines the prophecies about the American Indians into one concice chart.  Who are they?  What were the Prophecies of the gentiles coming?  Why were they destroyed as a people?  What is their future?  Laminated.</t>
+  </si>
+  <si>
+    <t>A 8.5' x 11" map of the United States with locations and events that transpired as church history unfolded.  It shows where each section of the D&amp;C was recieved. The back has the chronology of the early church history.  Laminated.</t>
+  </si>
+  <si>
+    <t>10 beautiful 12" x 18" yard signs with H-stakes showing titles and images of Jesus. Great for showing your love for Jesus Christ at Christmas, Easter, or anytime.  ($10 per sign)</t>
+  </si>
+  <si>
+    <t>This 8.5" x 11" chart explains the Abrahamic Covenant, who it is to and what it is.   Laminated.</t>
+  </si>
+  <si>
+    <t>10 pictures of Jesus with small snips from the pictures to match with the pictures, includes three levels of dificulty.</t>
+  </si>
+  <si>
+    <t>Happiness You Deserve Chart</t>
+  </si>
+  <si>
+    <t>Happiness You Deserve.jpg</t>
+  </si>
+  <si>
+    <t>Fill a Spirit World for Wards</t>
+  </si>
+  <si>
+    <t>A ward challenge. Can you do the temple work for enough people to fill a spirit world chapel? Add a dot for each ordinance done and see their chapel fill. Tracks 600 ordinances.</t>
+  </si>
+  <si>
+    <t>A family or individual challenge. Can you do the temple work for enough people to fill a spirit world chapel? Add a dot for each ordinance done and see their chapel fill in the spirit world. Tracks 150 ordinances.</t>
+  </si>
+  <si>
+    <t>Fill a Spirit World for Individuals or Families</t>
+  </si>
+  <si>
+    <t>4.75" x 7" bookmark shows family relationships for Abraham, Isaac, Jacob, &amp; his sons.  Shows from whom the Moabites, Edomites, &amp; Children of Ammon descended.  The back lists the scriptures that help define the Abrahamic covenant.  Laminated.</t>
+  </si>
+  <si>
+    <t>This 4.75" x 7" bookmark  shows a time line of Old Testament events and people.  It shows the patriarchs' births and how long they lived.  Identifies roles of the leaders in Israel and Judah. It also shows when each book of the Old Testament was written. Laminated.</t>
+  </si>
+  <si>
+    <t>This 4.75" x 7" bookmark condenses the Book of Revelations to provide a list of 107 events leading up to Christ's second coming.  Laminated.</t>
+  </si>
+  <si>
+    <t>This 4.75" x 7" bookmark lists all the miracles Jesus performed that are recorded in the New Testament with their references.    Laminated</t>
+  </si>
+  <si>
+    <t>This 4.75" x 7" bookmark lists all the parables of Jesus Christ that are recorded in the New Testament with their references.   Laminated.</t>
+  </si>
+  <si>
+    <t>This 4.75" x 7" bookmark summarizes D&amp;C 76 and contrasts the  telestial, terrestrial, and celestial kingdoms and shows the requirements and rewards for each kingdom.  Laminated.</t>
+  </si>
+  <si>
+    <t>This 4.75" x 7" bookmark lists many of the things that Joseph Smith did that are evidences that he truly was a prophet of God.   Laminated.</t>
+  </si>
+  <si>
+    <t>This 4.75" x 7" bookmark lists the miracles recorded in the Old Testament with their scripture references.  Laminated.</t>
+  </si>
+  <si>
+    <t>This 4.75" x 7" bookmark is designed as a quick reference for major events that happened in the Old Testament and their scripture references.  Laminated.</t>
+  </si>
+  <si>
+    <t>This 4.75" x 7" bookmark shows how Daniel in a vision saw the year when Joseph Smith would complete the restoration and “the sanctuary” would be cleansed.    Laminated.</t>
+  </si>
+  <si>
+    <t>This 4.75" x 7" bookmark lists many of the prophecies about Jesus Christ recorded in the Old Testament with their scripture references.  Laminated.</t>
+  </si>
+  <si>
+    <t>This 4.75" x 7" bookmark  lists many major events in the New Testament, their locations, and the scripture reference.    Laminated.</t>
+  </si>
+  <si>
+    <t>This 4.75" x 7" bookmark lists many evidences for the Book of Mormon.  Laminated.</t>
+  </si>
+  <si>
+    <t>4.75" x 7" bookmark Lists many of the miracles spoken of in the Book of Mormon.  Laminated.</t>
+  </si>
+  <si>
+    <t>A 4.75" x 7" bookmark that lists church doctrine and oft quoted scriptures and where to find them in the Doctrine and Covenants.  Laminated.</t>
+  </si>
+  <si>
+    <t>This 4.75" x 7" bookmark is designed as a pass along card to share LDS beliefs with those who would like to know more about the Church of Jesus Christ of Latter-day Saints. Laminated.</t>
+  </si>
+  <si>
+    <t>This 4.75" x 7" bookmark  lists the offices, quorums, and duties of the Aaronic &amp; Melchizedek Priesthood and includes the scripture references associated with each office.  Laminated.</t>
+  </si>
+  <si>
+    <t>This 4.75" x 7" bookmark lists 48 doctrines that were taught by Jesus and his disciples that should exist in His church today.  All references are from the Bible.  Laminated.</t>
+  </si>
+  <si>
+    <t>This 8.5" x 11" chart shows 129 prophecies in relationship to the church, the house of Israel, and the world in general.  A concise overview of the times we are living in and the signs of the second coming of Jesus Christ.  Laminated.</t>
+  </si>
+  <si>
+    <t>This is a complete 4 page list of scriptures that mention location in the Book of Mormon that relate to other locations. It was designed to help those who want a deep dive into the Book of Mormon geography.</t>
+  </si>
+  <si>
+    <t>8.5" x 11" chart shows family relationships for Abraham, Isaac, Jacob, &amp; his sons.  Shows from whom the Moabites, Edomites, &amp; Children of Ammon descended.   The back lists the scriptures that help define the Abrahamic covenant.  Laminated.</t>
+  </si>
+  <si>
+    <t>This 8.5" x 11" chart lists what we know of the lost tribes, where they went, where they are, when and how will they return.   Laminated.</t>
+  </si>
+  <si>
+    <t>8.5" x 11" chart list all the people in the Book of Mormon (non-Jaradite) in the chronological order they are mentioned.  It indicates their main roles and affiliations.  A great Book of Mormon overview and study help. Laminated.</t>
+  </si>
+  <si>
+    <t>MarriagePamphlet.jpg</t>
+  </si>
+  <si>
+    <t>FillOneChapel-Ward.jpg</t>
+  </si>
+  <si>
+    <t>FillaChapel.jpg</t>
   </si>
 </sst>
 </file>
@@ -897,13 +911,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7BF97CC-7DEE-4464-A48F-5AD6090A9F53}">
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H54"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.109375" customWidth="1"/>
     <col min="2" max="2" width="57.21875" customWidth="1"/>
     <col min="3" max="3" width="8.88671875" style="1"/>
-    <col min="4" max="4" width="20.33203125" customWidth="1"/>
+    <col min="4" max="4" width="23.109375" customWidth="1"/>
     <col min="5" max="5" width="33.21875" customWidth="1"/>
     <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="201.77734375" customWidth="1"/>
@@ -937,19 +951,19 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>67057900453</v>
+        <v>67057900900</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>105</v>
       </c>
       <c r="C2" s="1">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>108</v>
       </c>
       <c r="F2" t="s">
         <v>5</v>
@@ -958,50 +972,50 @@
         <v>5</v>
       </c>
       <c r="H2" t="s">
-        <v>13</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>67057900451</v>
+        <v>67057900495</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>74</v>
       </c>
       <c r="C3" s="1">
         <v>6</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="F3" t="s">
         <v>5</v>
       </c>
       <c r="G3" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H3" t="s">
-        <v>17</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>67057900550</v>
+        <v>67057900140</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="C4" s="1">
-        <v>19.95</v>
+        <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="E4" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="F4" t="s">
         <v>5</v>
@@ -1010,24 +1024,24 @@
         <v>7</v>
       </c>
       <c r="H4" t="s">
-        <v>19</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>67057900403</v>
+        <v>67057900416</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="C5" s="1">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E5" t="s">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="F5" t="s">
         <v>5</v>
@@ -1036,50 +1050,50 @@
         <v>7</v>
       </c>
       <c r="H5" t="s">
-        <v>70</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>67057900401</v>
+        <v>67057900420</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>6</v>
       </c>
       <c r="C6" s="1">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E6" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="F6" t="s">
         <v>5</v>
       </c>
       <c r="G6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H6" t="s">
-        <v>71</v>
+        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>67057900410</v>
+        <v>67057900402</v>
       </c>
       <c r="B7" t="s">
-        <v>137</v>
+        <v>59</v>
       </c>
       <c r="C7" s="1">
+        <v>2</v>
+      </c>
+      <c r="D7" t="s">
         <v>20</v>
       </c>
-      <c r="D7" t="s">
-        <v>22</v>
-      </c>
       <c r="E7" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="F7" t="s">
         <v>5</v>
@@ -1088,24 +1102,24 @@
         <v>7</v>
       </c>
       <c r="H7" t="s">
-        <v>138</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>67057900402</v>
+        <v>67057900417</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="C8" s="1">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E8" t="s">
-        <v>74</v>
+        <v>93</v>
       </c>
       <c r="F8" t="s">
         <v>5</v>
@@ -1114,24 +1128,24 @@
         <v>7</v>
       </c>
       <c r="H8" t="s">
-        <v>70</v>
+        <v>154</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>67057900420</v>
+        <v>67057900210</v>
       </c>
       <c r="B9" t="s">
-        <v>6</v>
+        <v>125</v>
       </c>
       <c r="C9" s="1">
-        <v>3.5</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>63</v>
       </c>
       <c r="F9" t="s">
         <v>5</v>
@@ -1140,24 +1154,24 @@
         <v>5</v>
       </c>
       <c r="H9" t="s">
-        <v>24</v>
+        <v>132</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>67057900486</v>
+        <v>67057900444</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C10" s="1">
         <v>3.5</v>
       </c>
       <c r="D10" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="E10" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="F10" t="s">
         <v>5</v>
@@ -1166,50 +1180,50 @@
         <v>5</v>
       </c>
       <c r="H10" t="s">
-        <v>28</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>67057900487</v>
+        <v>67057900443</v>
       </c>
       <c r="B11" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="C11" s="1">
         <v>6</v>
       </c>
       <c r="D11" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="E11" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="F11" t="s">
         <v>5</v>
       </c>
       <c r="G11" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H11" t="s">
-        <v>28</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>67057900425</v>
+        <v>67057900225</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>123</v>
       </c>
       <c r="C12" s="1">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="D12" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="E12" t="s">
-        <v>30</v>
+        <v>120</v>
       </c>
       <c r="F12" t="s">
         <v>5</v>
@@ -1218,76 +1232,76 @@
         <v>5</v>
       </c>
       <c r="H12" t="s">
-        <v>31</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>67057900441</v>
+        <v>67057900463</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>82</v>
       </c>
       <c r="C13" s="1">
         <v>3.5</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E13" t="s">
-        <v>34</v>
+        <v>83</v>
       </c>
       <c r="F13" t="s">
         <v>5</v>
       </c>
       <c r="G13" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H13" t="s">
-        <v>37</v>
+        <v>150</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>67057900440</v>
+        <v>67057900407</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>111</v>
       </c>
       <c r="C14" s="1">
         <v>6</v>
       </c>
       <c r="D14" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="E14" t="s">
-        <v>34</v>
+        <v>113</v>
       </c>
       <c r="F14" t="s">
         <v>5</v>
       </c>
       <c r="G14" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H14" t="s">
-        <v>36</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>67057900435</v>
+        <v>67057900550</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="C15" s="1">
-        <v>3.5</v>
+        <v>19.95</v>
       </c>
       <c r="D15" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="E15" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="F15" t="s">
         <v>5</v>
@@ -1296,24 +1310,24 @@
         <v>7</v>
       </c>
       <c r="H15" t="s">
-        <v>40</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>67057900437</v>
+        <v>67057900414</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C16" s="1">
         <v>3.5</v>
       </c>
       <c r="D16" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="F16" t="s">
         <v>5</v>
@@ -1322,24 +1336,24 @@
         <v>7</v>
       </c>
       <c r="H16" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>67057900484</v>
+        <v>67057900482</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C17" s="1">
         <v>3.5</v>
       </c>
       <c r="D17" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="E17" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="F17" t="s">
         <v>5</v>
@@ -1348,24 +1362,24 @@
         <v>7</v>
       </c>
       <c r="H17" t="s">
-        <v>46</v>
+        <v>146</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>67057900416</v>
+        <v>67057900431</v>
       </c>
       <c r="B18" t="s">
-        <v>47</v>
+        <v>80</v>
       </c>
       <c r="C18" s="1">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="D18" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E18" t="s">
-        <v>48</v>
+        <v>81</v>
       </c>
       <c r="F18" t="s">
         <v>5</v>
@@ -1374,24 +1388,24 @@
         <v>7</v>
       </c>
       <c r="H18" t="s">
-        <v>49</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>67057900456</v>
+        <v>67057900460</v>
       </c>
       <c r="B19" t="s">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="C19" s="1">
         <v>3.5</v>
       </c>
       <c r="D19" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E19" t="s">
-        <v>51</v>
+        <v>91</v>
       </c>
       <c r="F19" t="s">
         <v>5</v>
@@ -1400,24 +1414,24 @@
         <v>5</v>
       </c>
       <c r="H19" t="s">
-        <v>52</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>67057900458</v>
+        <v>67057900461</v>
       </c>
       <c r="B20" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C20" s="1">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="D20" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="E20" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F20" t="s">
         <v>5</v>
@@ -1426,24 +1440,24 @@
         <v>5</v>
       </c>
       <c r="H20" t="s">
-        <v>54</v>
+        <v>147</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>67057900414</v>
+        <v>67057900499</v>
       </c>
       <c r="B21" t="s">
-        <v>55</v>
+        <v>140</v>
       </c>
       <c r="C21" s="1">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="D21" t="s">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="E21" t="s">
-        <v>20</v>
+        <v>166</v>
       </c>
       <c r="F21" t="s">
         <v>5</v>
@@ -1452,50 +1466,50 @@
         <v>7</v>
       </c>
       <c r="H21" t="s">
-        <v>56</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>67057900444</v>
+        <v>67057900498</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>137</v>
       </c>
       <c r="C22" s="1">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="D22" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="E22" t="s">
-        <v>59</v>
+        <v>165</v>
       </c>
       <c r="F22" t="s">
         <v>5</v>
       </c>
       <c r="G22" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H22" t="s">
-        <v>62</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>67057900443</v>
+        <v>67057900130</v>
       </c>
       <c r="B23" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C23" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D23" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E23" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="F23" t="s">
         <v>5</v>
@@ -1504,24 +1518,24 @@
         <v>7</v>
       </c>
       <c r="H23" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>67057900482</v>
+        <v>67057900301</v>
       </c>
       <c r="B24" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C24" s="1">
-        <v>3.5</v>
+        <v>7</v>
       </c>
       <c r="D24" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="E24" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="F24" t="s">
         <v>5</v>
@@ -1530,76 +1544,76 @@
         <v>7</v>
       </c>
       <c r="H24" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>67057900461</v>
+        <v>67057900486</v>
       </c>
       <c r="B25" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="C25" s="1">
         <v>3.5</v>
       </c>
       <c r="D25" t="s">
-        <v>58</v>
+        <v>23</v>
       </c>
       <c r="E25" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="F25" t="s">
         <v>5</v>
       </c>
       <c r="G25" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H25" t="s">
-        <v>68</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>67057900210</v>
+        <v>67057900487</v>
       </c>
       <c r="B26" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="C26" s="1">
-        <v>99</v>
+        <v>6</v>
       </c>
       <c r="D26" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E26" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="F26" t="s">
         <v>5</v>
       </c>
       <c r="G26" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H26" t="s">
-        <v>112</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>67057900140</v>
+        <v>67057900497</v>
       </c>
       <c r="B27" t="s">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="C27" s="1">
-        <v>8</v>
+        <v>2.5</v>
       </c>
       <c r="D27" t="s">
-        <v>78</v>
+        <v>12</v>
       </c>
       <c r="E27" t="s">
-        <v>80</v>
+        <v>136</v>
       </c>
       <c r="F27" t="s">
         <v>5</v>
@@ -1608,50 +1622,50 @@
         <v>7</v>
       </c>
       <c r="H27" t="s">
-        <v>81</v>
+        <v>118</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>67057900130</v>
+        <v>67057900480</v>
       </c>
       <c r="B28" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C28" s="1">
-        <v>9</v>
+        <v>3.5</v>
       </c>
       <c r="D28" t="s">
-        <v>78</v>
+        <v>12</v>
       </c>
       <c r="E28" t="s">
-        <v>83</v>
+        <v>109</v>
       </c>
       <c r="F28" t="s">
         <v>5</v>
       </c>
       <c r="G28" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H28" t="s">
-        <v>84</v>
+        <v>156</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>67057900301</v>
+        <v>67057900481</v>
       </c>
       <c r="B29" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="C29" s="1">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D29" t="s">
-        <v>78</v>
+        <v>12</v>
       </c>
       <c r="E29" t="s">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="F29" t="s">
         <v>5</v>
@@ -1660,24 +1674,24 @@
         <v>7</v>
       </c>
       <c r="H29" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>67057900495</v>
+        <v>67057900488</v>
       </c>
       <c r="B30" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C30" s="1">
         <v>6</v>
       </c>
       <c r="D30" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E30" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="F30" t="s">
         <v>5</v>
@@ -1686,24 +1700,24 @@
         <v>7</v>
       </c>
       <c r="H30" t="s">
-        <v>90</v>
+        <v>162</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>67057900488</v>
+        <v>67057900491</v>
       </c>
       <c r="B31" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="C31" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D31" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="E31" t="s">
-        <v>92</v>
+        <v>164</v>
       </c>
       <c r="F31" t="s">
         <v>5</v>
@@ -1712,7 +1726,7 @@
         <v>7</v>
       </c>
       <c r="H31" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
@@ -1720,16 +1734,16 @@
         <v>67057900472</v>
       </c>
       <c r="B32" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="C32" s="1">
         <v>3.5</v>
       </c>
       <c r="D32" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E32" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="F32" t="s">
         <v>5</v>
@@ -1738,24 +1752,24 @@
         <v>7</v>
       </c>
       <c r="H32" t="s">
-        <v>96</v>
+        <v>148</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>67057900431</v>
+        <v>67057900437</v>
       </c>
       <c r="B33" t="s">
-        <v>97</v>
+        <v>34</v>
       </c>
       <c r="C33" s="1">
         <v>3.5</v>
       </c>
       <c r="D33" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E33" t="s">
-        <v>98</v>
+        <v>35</v>
       </c>
       <c r="F33" t="s">
         <v>5</v>
@@ -1764,24 +1778,24 @@
         <v>7</v>
       </c>
       <c r="H33" t="s">
-        <v>99</v>
+        <v>144</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>67057900463</v>
+        <v>67057900427</v>
       </c>
       <c r="B34" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="C34" s="1">
         <v>3.5</v>
       </c>
       <c r="D34" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E34" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="F34" t="s">
         <v>5</v>
@@ -1790,50 +1804,50 @@
         <v>7</v>
       </c>
       <c r="H34" t="s">
-        <v>102</v>
+        <v>152</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>67057900470</v>
+        <v>67057900441</v>
       </c>
       <c r="B35" t="s">
-        <v>103</v>
+        <v>27</v>
       </c>
       <c r="C35" s="1">
         <v>3.5</v>
       </c>
       <c r="D35" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E35" t="s">
-        <v>104</v>
+        <v>29</v>
       </c>
       <c r="F35" t="s">
         <v>5</v>
       </c>
       <c r="G35" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H35" t="s">
-        <v>105</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>67057900427</v>
+        <v>67057900440</v>
       </c>
       <c r="B36" t="s">
-        <v>106</v>
+        <v>30</v>
       </c>
       <c r="C36" s="1">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="D36" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="E36" t="s">
-        <v>107</v>
+        <v>29</v>
       </c>
       <c r="F36" t="s">
         <v>5</v>
@@ -1842,50 +1856,50 @@
         <v>7</v>
       </c>
       <c r="H36" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>67057900464</v>
+        <v>67057900425</v>
       </c>
       <c r="B37" t="s">
-        <v>109</v>
+        <v>25</v>
       </c>
       <c r="C37" s="1">
         <v>3.5</v>
       </c>
       <c r="D37" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="E37" t="s">
-        <v>110</v>
+        <v>26</v>
       </c>
       <c r="F37" t="s">
         <v>5</v>
       </c>
       <c r="G37" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H37" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>67057900460</v>
+        <v>67057900435</v>
       </c>
       <c r="B38" t="s">
-        <v>113</v>
+        <v>32</v>
       </c>
       <c r="C38" s="1">
         <v>3.5</v>
       </c>
       <c r="D38" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E38" t="s">
-        <v>114</v>
+        <v>33</v>
       </c>
       <c r="F38" t="s">
         <v>5</v>
@@ -1894,24 +1908,24 @@
         <v>7</v>
       </c>
       <c r="H38" t="s">
-        <v>115</v>
+        <v>145</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>67057900417</v>
+        <v>67057900418</v>
       </c>
       <c r="B39" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="C39" s="1">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="D39" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E39" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="F39" t="s">
         <v>5</v>
@@ -1920,24 +1934,24 @@
         <v>7</v>
       </c>
       <c r="H39" t="s">
-        <v>118</v>
+        <v>163</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>67057900418</v>
+        <v>67057900462</v>
       </c>
       <c r="B40" t="s">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="C40" s="1">
         <v>6</v>
       </c>
       <c r="D40" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="E40" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
       <c r="F40" t="s">
         <v>5</v>
@@ -1946,50 +1960,50 @@
         <v>7</v>
       </c>
       <c r="H40" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>67057900445</v>
+        <v>67057900456</v>
       </c>
       <c r="B41" t="s">
-        <v>124</v>
+        <v>40</v>
       </c>
       <c r="C41" s="1">
         <v>3.5</v>
       </c>
       <c r="D41" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="E41" t="s">
-        <v>122</v>
+        <v>41</v>
       </c>
       <c r="F41" t="s">
         <v>5</v>
       </c>
       <c r="G41" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H41" t="s">
-        <v>123</v>
+        <v>42</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>67057900466</v>
+        <v>67057900458</v>
       </c>
       <c r="B42" t="s">
-        <v>125</v>
+        <v>43</v>
       </c>
       <c r="C42" s="1">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="D42" t="s">
-        <v>58</v>
+        <v>12</v>
       </c>
       <c r="E42" t="s">
-        <v>126</v>
+        <v>41</v>
       </c>
       <c r="F42" t="s">
         <v>5</v>
@@ -1998,24 +2012,24 @@
         <v>7</v>
       </c>
       <c r="H42" t="s">
-        <v>127</v>
+        <v>44</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>67057900462</v>
+        <v>67057900464</v>
       </c>
       <c r="B43" t="s">
-        <v>128</v>
+        <v>88</v>
       </c>
       <c r="C43" s="1">
-        <v>6</v>
+        <v>3.5</v>
       </c>
       <c r="D43" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E43" t="s">
-        <v>129</v>
+        <v>89</v>
       </c>
       <c r="F43" t="s">
         <v>5</v>
@@ -2024,24 +2038,24 @@
         <v>7</v>
       </c>
       <c r="H43" t="s">
-        <v>130</v>
+        <v>158</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>67057900480</v>
+        <v>67057900466</v>
       </c>
       <c r="B44" t="s">
-        <v>131</v>
+        <v>98</v>
       </c>
       <c r="C44" s="1">
         <v>3.5</v>
       </c>
       <c r="D44" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="E44" t="s">
-        <v>142</v>
+        <v>99</v>
       </c>
       <c r="F44" t="s">
         <v>5</v>
@@ -2050,24 +2064,24 @@
         <v>7</v>
       </c>
       <c r="H44" t="s">
-        <v>132</v>
+        <v>157</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>67057900481</v>
+        <v>67057900470</v>
       </c>
       <c r="B45" t="s">
-        <v>133</v>
+        <v>84</v>
       </c>
       <c r="C45" s="1">
-        <v>10</v>
+        <v>3.5</v>
       </c>
       <c r="D45" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="E45" t="s">
-        <v>142</v>
+        <v>85</v>
       </c>
       <c r="F45" t="s">
         <v>5</v>
@@ -2076,24 +2090,24 @@
         <v>7</v>
       </c>
       <c r="H45" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>67057900900</v>
+        <v>67057900250</v>
       </c>
       <c r="B46" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="C46" s="1">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D46" t="s">
         <v>12</v>
       </c>
       <c r="E46" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="F46" t="s">
         <v>5</v>
@@ -2102,50 +2116,50 @@
         <v>5</v>
       </c>
       <c r="H46" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>67057900910</v>
+        <v>67057900445</v>
       </c>
       <c r="B47" t="s">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="C47" s="1">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="D47" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="E47" t="s">
-        <v>146</v>
+        <v>96</v>
       </c>
       <c r="F47" t="s">
         <v>5</v>
       </c>
       <c r="G47" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H47" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>67057900407</v>
+        <v>67057900484</v>
       </c>
       <c r="B48" t="s">
-        <v>145</v>
+        <v>36</v>
       </c>
       <c r="C48" s="1">
-        <v>5.99</v>
+        <v>3.5</v>
       </c>
       <c r="D48" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E48" t="s">
-        <v>147</v>
+        <v>37</v>
       </c>
       <c r="F48" t="s">
         <v>5</v>
@@ -2154,102 +2168,102 @@
         <v>7</v>
       </c>
       <c r="H48" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>67057900225</v>
+        <v>67057900910</v>
       </c>
       <c r="B49" t="s">
-        <v>143</v>
+        <v>124</v>
       </c>
       <c r="C49" s="1">
-        <v>5.99</v>
+        <v>5</v>
       </c>
       <c r="D49" t="s">
         <v>12</v>
       </c>
       <c r="E49" t="s">
-        <v>158</v>
+        <v>112</v>
       </c>
       <c r="F49" t="s">
         <v>5</v>
       </c>
       <c r="G49" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H49" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>67057900250</v>
+        <v>67057900453</v>
       </c>
       <c r="B50" t="s">
-        <v>140</v>
+        <v>11</v>
       </c>
       <c r="C50" s="1">
-        <v>9.99</v>
+        <v>3.5</v>
       </c>
       <c r="D50" t="s">
         <v>12</v>
       </c>
       <c r="E50" t="s">
-        <v>161</v>
+        <v>14</v>
       </c>
       <c r="F50" t="s">
         <v>5</v>
       </c>
       <c r="G50" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H50" t="s">
-        <v>152</v>
+        <v>13</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>67057900491</v>
+        <v>67057900451</v>
       </c>
       <c r="B51" t="s">
-        <v>144</v>
+        <v>15</v>
       </c>
       <c r="C51" s="1">
-        <v>1.99</v>
+        <v>6</v>
       </c>
       <c r="D51" t="s">
         <v>12</v>
       </c>
       <c r="E51" t="s">
-        <v>148</v>
+        <v>16</v>
       </c>
       <c r="F51" t="s">
         <v>5</v>
       </c>
       <c r="G51" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H51" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>67057900497</v>
+        <v>67057900403</v>
       </c>
       <c r="B52" t="s">
-        <v>136</v>
+        <v>19</v>
       </c>
       <c r="C52" s="1">
-        <v>2.4900000000000002</v>
+        <v>3.5</v>
       </c>
       <c r="D52" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E52" t="s">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="F52" t="s">
         <v>5</v>
@@ -2258,24 +2272,24 @@
         <v>7</v>
       </c>
       <c r="H52" t="s">
-        <v>154</v>
+        <v>57</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>67057900498</v>
+        <v>67057900401</v>
       </c>
       <c r="B53" t="s">
-        <v>157</v>
+        <v>56</v>
       </c>
       <c r="C53" s="1">
-        <v>19.989999999999998</v>
+        <v>6</v>
       </c>
       <c r="D53" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="E53" t="s">
-        <v>159</v>
+        <v>60</v>
       </c>
       <c r="F53" t="s">
         <v>5</v>
@@ -2284,10 +2298,40 @@
         <v>7</v>
       </c>
       <c r="H53" t="s">
-        <v>155</v>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>67057900410</v>
+      </c>
+      <c r="B54" t="s">
+        <v>106</v>
+      </c>
+      <c r="C54" s="1">
+        <v>20</v>
+      </c>
+      <c r="D54" t="s">
+        <v>20</v>
+      </c>
+      <c r="E54" t="s">
+        <v>60</v>
+      </c>
+      <c r="F54" t="s">
+        <v>5</v>
+      </c>
+      <c r="G54" t="s">
+        <v>7</v>
+      </c>
+      <c r="H54" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H54">
+    <sortCondition ref="E5:E54"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>